--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F576DE58-0242-422D-9C8F-DC9918327408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936AF36739C8470D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75C0A87B-4A5A-4E5A-A311-0E23DB545289}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 14-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936AF36739C8470D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75C0A87B-4A5A-4E5A-A311-0E23DB545289}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936475EF797DA70D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AF5179-AA62-4914-9058-9AAB48EA0497}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936475EF797DA70D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AF5179-AA62-4914-9058-9AAB48EA0497}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CBADC1-B386-4D91-8FA9-36FFD32E580A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CBADC1-B386-4D91-8FA9-36FFD32E580A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A99A4-A014-4C1F-A1E3-7A2038CDE01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 14-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 17-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A99A4-A014-4C1F-A1E3-7A2038CDE01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B88877E-B49F-4D94-89A3-57C481E9B0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B88877E-B49F-4D94-89A3-57C481E9B0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD89367C3E729D6870D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BC8B3E-5126-4045-BDB7-E128C2C0A3DB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 17-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 18-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD89367C3E729D6870D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BC8B3E-5126-4045-BDB7-E128C2C0A3DB}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD89366EBE74A86070D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D1DA5D-6B39-4946-99CA-5992D7E16699}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 18-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 21-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD89366EBE74A86070D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D1DA5D-6B39-4946-99CA-5992D7E16699}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31047752-F26B-4458-8233-F95AFA8D34D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31047752-F26B-4458-8233-F95AFA8D34D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833961E9-0499-456E-BE3C-1A0842BD2859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 21-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833961E9-0499-456E-BE3C-1A0842BD2859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372953C9-465A-4CE6-AF1D-F0FF71D67C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372953C9-465A-4CE6-AF1D-F0FF71D67C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCC720F-39CF-4841-B55D-C3E61DF58ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCC720F-39CF-4841-B55D-C3E61DF58ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936563E73AAC070D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA3C0B3-D469-4163-B334-9313A7DD6809}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91A25F2BBBD8936563E73AAC070D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA3C0B3-D469-4163-B334-9313A7DD6809}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936DF6634959671D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861345DE-69F7-49C7-A34F-1EEB2F537389}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 24-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,7 +55,7 @@
     <t>Godkendt</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936DF6634959671D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861345DE-69F7-49C7-A34F-1EEB2F537389}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936AF9E37A2A871D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54946BB1-8576-44DD-B601-1C8D3ABA1843}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936AF9E37A2A871D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54946BB1-8576-44DD-B601-1C8D3ABA1843}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EAB49A-2D52-4AAD-A6AD-8D6C1C21B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 24-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 28-09-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EAB49A-2D52-4AAD-A6AD-8D6C1C21B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE73893634E635A55E71D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE76F986-A446-4E84-B541-6E9A9C655C64}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 28-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372953C9-465A-4CE6-AF1D-F0FF71D67C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA1743-8141-4BCC-AB5D-7E4BEF88672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 22-09-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,7 +55,7 @@
     <t>Godkendt</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE73893634E635A55E71D82230" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE76F986-A446-4E84-B541-6E9A9C655C64}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CE97AC-F1F3-498D-9E77-DDE124508E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 02-10-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -842,9 +842,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F111"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>110</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>116</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>58</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>125</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>127</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>61</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>71</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>75</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>139</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>93</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>149</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>151</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>157</v>
       </c>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CE97AC-F1F3-498D-9E77-DDE124508E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936240671BC2A71D8223C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A195729-B244-4347-BA2A-B5CE81E19257}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 07-10-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 08-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936240671BC2A71D8223C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A195729-B244-4347-BA2A-B5CE81E19257}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE36D3E-4397-492C-BFDC-79DB7EA464AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 08-10-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE36D3E-4397-492C-BFDC-79DB7EA464AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3329ABE0-6770-450D-8F28-4D6E5FE168A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-EPJ-systemer_excel.XLSX
+++ b/html/Sygehus-EPJ-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3329ABE0-6770-450D-8F28-4D6E5FE168A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB91F8532AE738936DF8EB0A39071D8223C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{509F9A8E-2019-4740-BDB4-87656B49B2C2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 09-10-2026'!$A$1:$F$111</definedName>
+    <definedName name="Sygehus_EPJ_systemer">'Opdateret d. 23-10-2026'!$A$1:$F$111</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
